--- a/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches.xlsx
+++ b/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches.xlsx
@@ -1,37 +1,295 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="81">
+  <si>
+    <t>left_iri</t>
+  </si>
+  <si>
+    <t>left_label</t>
+  </si>
+  <si>
+    <t>left_shape</t>
+  </si>
+  <si>
+    <t>left_axioms</t>
+  </si>
+  <si>
+    <t>right_iri</t>
+  </si>
+  <si>
+    <t>right_label</t>
+  </si>
+  <si>
+    <t>right_shape</t>
+  </si>
+  <si>
+    <t>right_axioms</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000011</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000028</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000009</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000004</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000040</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000029</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000015</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000018</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000140</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000148</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000006</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000147</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000026</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000002</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000142</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000035</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000146</t>
+  </si>
+  <si>
+    <t>spatiotemporal region</t>
+  </si>
+  <si>
+    <t>three-dimensional spatial region</t>
+  </si>
+  <si>
+    <t>two-dimensional spatial region</t>
+  </si>
+  <si>
+    <t>independent continuant</t>
+  </si>
+  <si>
+    <t>material entity</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>zero-dimensional spatial region</t>
+  </si>
+  <si>
+    <t>temporal region</t>
+  </si>
+  <si>
+    <t>continuant fiat boundary</t>
+  </si>
+  <si>
+    <t>one-dimensional temporal region</t>
+  </si>
+  <si>
+    <t>zero-dimensional temporal region</t>
+  </si>
+  <si>
+    <t>spatial region</t>
+  </si>
+  <si>
+    <t>fiat point</t>
+  </si>
+  <si>
+    <t>one-dimensional spatial region</t>
+  </si>
+  <si>
+    <t>continuant</t>
+  </si>
+  <si>
+    <t>fiat line</t>
+  </si>
+  <si>
+    <t>process boundary</t>
+  </si>
+  <si>
+    <t>fiat surface</t>
+  </si>
+  <si>
+    <t>R:only×2</t>
+  </si>
+  <si>
+    <t>R:only</t>
+  </si>
+  <si>
+    <t>R:only×3</t>
+  </si>
+  <si>
+    <t>R:only×4</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000011 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000011</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000006</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000009 OR ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000002 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000004</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000004 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000040 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000040 OR ns1:BFO_0000140)</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only (ns1:BFO_0000029 OR ns1:BFO_0000040) | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000140) | SubClassOf: ns1:BFO_0000210 only ns1:BFO_0000028</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000015 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000015</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000018</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000008</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000124 only ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only (ns1:BFO_0000038 OR ns1:BFO_0000148) | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000038</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000148</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000006</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000147</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000001 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000002</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000142 OR ns1:BFO_0000147)</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000132 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000139 only (ns1:BFO_0000015 OR ns1:BFO_0000035)</t>
+  </si>
+  <si>
+    <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+  </si>
+  <si>
+    <t>Account Holder</t>
+  </si>
+  <si>
+    <t>Money Transfer</t>
+  </si>
+  <si>
+    <t>Responsible Actor State</t>
+  </si>
+  <si>
+    <t>Radio Mast</t>
+  </si>
+  <si>
+    <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+  </si>
+  <si>
+    <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+  </si>
+  <si>
+    <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+  </si>
+  <si>
+    <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +304,41 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,57 +626,2167 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H77"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>left_iri</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>left_label</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>left_shape</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>left_axioms</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>right_iri</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>right_label</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>right_shape</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>right_axioms</t>
-        </is>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" t="s">
+        <v>73</v>
+      </c>
+      <c r="G42" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" t="s">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" t="s">
+        <v>73</v>
+      </c>
+      <c r="G50" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" t="s">
+        <v>74</v>
+      </c>
+      <c r="G51" t="s">
+        <v>47</v>
+      </c>
+      <c r="H51" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" t="s">
+        <v>75</v>
+      </c>
+      <c r="G52" t="s">
+        <v>47</v>
+      </c>
+      <c r="H52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" t="s">
+        <v>47</v>
+      </c>
+      <c r="H54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G55" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" t="s">
+        <v>75</v>
+      </c>
+      <c r="G56" t="s">
+        <v>47</v>
+      </c>
+      <c r="H56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" t="s">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s">
+        <v>47</v>
+      </c>
+      <c r="H57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" t="s">
+        <v>73</v>
+      </c>
+      <c r="G58" t="s">
+        <v>47</v>
+      </c>
+      <c r="H58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F59" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59" t="s">
+        <v>47</v>
+      </c>
+      <c r="H59" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" t="s">
+        <v>75</v>
+      </c>
+      <c r="G60" t="s">
+        <v>47</v>
+      </c>
+      <c r="H60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s">
+        <v>47</v>
+      </c>
+      <c r="H61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F62" t="s">
+        <v>73</v>
+      </c>
+      <c r="G62" t="s">
+        <v>47</v>
+      </c>
+      <c r="H62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" t="s">
+        <v>65</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F63" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" t="s">
+        <v>47</v>
+      </c>
+      <c r="H63" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" t="s">
+        <v>65</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" t="s">
+        <v>75</v>
+      </c>
+      <c r="G64" t="s">
+        <v>47</v>
+      </c>
+      <c r="H64" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" t="s">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s">
+        <v>47</v>
+      </c>
+      <c r="H65" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F66" t="s">
+        <v>73</v>
+      </c>
+      <c r="G66" t="s">
+        <v>47</v>
+      </c>
+      <c r="H66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F67" t="s">
+        <v>74</v>
+      </c>
+      <c r="G67" t="s">
+        <v>47</v>
+      </c>
+      <c r="H67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B68" t="s">
+        <v>43</v>
+      </c>
+      <c r="C68" t="s">
+        <v>47</v>
+      </c>
+      <c r="D68" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F68" t="s">
+        <v>75</v>
+      </c>
+      <c r="G68" t="s">
+        <v>47</v>
+      </c>
+      <c r="H68" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>47</v>
+      </c>
+      <c r="D69" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" t="s">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s">
+        <v>47</v>
+      </c>
+      <c r="H69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" t="s">
+        <v>67</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" t="s">
+        <v>73</v>
+      </c>
+      <c r="G70" t="s">
+        <v>47</v>
+      </c>
+      <c r="H70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F71" t="s">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s">
+        <v>47</v>
+      </c>
+      <c r="H71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F72" t="s">
+        <v>75</v>
+      </c>
+      <c r="G72" t="s">
+        <v>47</v>
+      </c>
+      <c r="H72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F73" t="s">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s">
+        <v>47</v>
+      </c>
+      <c r="H73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" t="s">
+        <v>47</v>
+      </c>
+      <c r="D74" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" t="s">
+        <v>73</v>
+      </c>
+      <c r="G74" t="s">
+        <v>47</v>
+      </c>
+      <c r="H74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" t="s">
+        <v>47</v>
+      </c>
+      <c r="D75" t="s">
+        <v>68</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" t="s">
+        <v>74</v>
+      </c>
+      <c r="G75" t="s">
+        <v>47</v>
+      </c>
+      <c r="H75" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" t="s">
+        <v>47</v>
+      </c>
+      <c r="D76" t="s">
+        <v>68</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" t="s">
+        <v>75</v>
+      </c>
+      <c r="G76" t="s">
+        <v>47</v>
+      </c>
+      <c r="H76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s">
+        <v>47</v>
+      </c>
+      <c r="H77" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="E2" r:id="rId2" location="AccountHolder"/>
+    <hyperlink ref="A3" r:id="rId3"/>
+    <hyperlink ref="E3" r:id="rId4" location="MoneyTransfer"/>
+    <hyperlink ref="A4" r:id="rId5"/>
+    <hyperlink ref="E4" r:id="rId6" location="ResponsibleActorState"/>
+    <hyperlink ref="A5" r:id="rId7"/>
+    <hyperlink ref="E5" r:id="rId8" location="RadioMast"/>
+    <hyperlink ref="A6" r:id="rId9"/>
+    <hyperlink ref="E6" r:id="rId10" location="AccountHolder"/>
+    <hyperlink ref="A7" r:id="rId11"/>
+    <hyperlink ref="E7" r:id="rId12" location="MoneyTransfer"/>
+    <hyperlink ref="A8" r:id="rId13"/>
+    <hyperlink ref="E8" r:id="rId14" location="ResponsibleActorState"/>
+    <hyperlink ref="A9" r:id="rId15"/>
+    <hyperlink ref="E9" r:id="rId16" location="RadioMast"/>
+    <hyperlink ref="A10" r:id="rId17"/>
+    <hyperlink ref="E10" r:id="rId18" location="AccountHolder"/>
+    <hyperlink ref="A11" r:id="rId19"/>
+    <hyperlink ref="E11" r:id="rId20" location="MoneyTransfer"/>
+    <hyperlink ref="A12" r:id="rId21"/>
+    <hyperlink ref="E12" r:id="rId22" location="ResponsibleActorState"/>
+    <hyperlink ref="A13" r:id="rId23"/>
+    <hyperlink ref="E13" r:id="rId24" location="RadioMast"/>
+    <hyperlink ref="A14" r:id="rId25"/>
+    <hyperlink ref="E14" r:id="rId26" location="AccountHolder"/>
+    <hyperlink ref="A15" r:id="rId27"/>
+    <hyperlink ref="E15" r:id="rId28" location="MoneyTransfer"/>
+    <hyperlink ref="A16" r:id="rId29"/>
+    <hyperlink ref="E16" r:id="rId30" location="ResponsibleActorState"/>
+    <hyperlink ref="A17" r:id="rId31"/>
+    <hyperlink ref="E17" r:id="rId32" location="RadioMast"/>
+    <hyperlink ref="A18" r:id="rId33"/>
+    <hyperlink ref="E18" r:id="rId34" location="AccountHolder"/>
+    <hyperlink ref="A19" r:id="rId35"/>
+    <hyperlink ref="E19" r:id="rId36" location="MoneyTransfer"/>
+    <hyperlink ref="A20" r:id="rId37"/>
+    <hyperlink ref="E20" r:id="rId38" location="ResponsibleActorState"/>
+    <hyperlink ref="A21" r:id="rId39"/>
+    <hyperlink ref="E21" r:id="rId40" location="RadioMast"/>
+    <hyperlink ref="A22" r:id="rId41"/>
+    <hyperlink ref="E22" r:id="rId42" location="AccountHolder"/>
+    <hyperlink ref="A23" r:id="rId43"/>
+    <hyperlink ref="E23" r:id="rId44" location="MoneyTransfer"/>
+    <hyperlink ref="A24" r:id="rId45"/>
+    <hyperlink ref="E24" r:id="rId46" location="ResponsibleActorState"/>
+    <hyperlink ref="A25" r:id="rId47"/>
+    <hyperlink ref="E25" r:id="rId48" location="RadioMast"/>
+    <hyperlink ref="A26" r:id="rId49"/>
+    <hyperlink ref="E26" r:id="rId50" location="AccountHolder"/>
+    <hyperlink ref="A27" r:id="rId51"/>
+    <hyperlink ref="E27" r:id="rId52" location="MoneyTransfer"/>
+    <hyperlink ref="A28" r:id="rId53"/>
+    <hyperlink ref="E28" r:id="rId54" location="ResponsibleActorState"/>
+    <hyperlink ref="A29" r:id="rId55"/>
+    <hyperlink ref="E29" r:id="rId56" location="RadioMast"/>
+    <hyperlink ref="A30" r:id="rId57"/>
+    <hyperlink ref="E30" r:id="rId58" location="AccountHolder"/>
+    <hyperlink ref="A31" r:id="rId59"/>
+    <hyperlink ref="E31" r:id="rId60" location="MoneyTransfer"/>
+    <hyperlink ref="A32" r:id="rId61"/>
+    <hyperlink ref="E32" r:id="rId62" location="ResponsibleActorState"/>
+    <hyperlink ref="A33" r:id="rId63"/>
+    <hyperlink ref="E33" r:id="rId64" location="RadioMast"/>
+    <hyperlink ref="A34" r:id="rId65"/>
+    <hyperlink ref="E34" r:id="rId66" location="AccountHolder"/>
+    <hyperlink ref="A35" r:id="rId67"/>
+    <hyperlink ref="E35" r:id="rId68" location="MoneyTransfer"/>
+    <hyperlink ref="A36" r:id="rId69"/>
+    <hyperlink ref="E36" r:id="rId70" location="ResponsibleActorState"/>
+    <hyperlink ref="A37" r:id="rId71"/>
+    <hyperlink ref="E37" r:id="rId72" location="RadioMast"/>
+    <hyperlink ref="A38" r:id="rId73"/>
+    <hyperlink ref="E38" r:id="rId74" location="AccountHolder"/>
+    <hyperlink ref="A39" r:id="rId75"/>
+    <hyperlink ref="E39" r:id="rId76" location="MoneyTransfer"/>
+    <hyperlink ref="A40" r:id="rId77"/>
+    <hyperlink ref="E40" r:id="rId78" location="ResponsibleActorState"/>
+    <hyperlink ref="A41" r:id="rId79"/>
+    <hyperlink ref="E41" r:id="rId80" location="RadioMast"/>
+    <hyperlink ref="A42" r:id="rId81"/>
+    <hyperlink ref="E42" r:id="rId82" location="AccountHolder"/>
+    <hyperlink ref="A43" r:id="rId83"/>
+    <hyperlink ref="E43" r:id="rId84" location="MoneyTransfer"/>
+    <hyperlink ref="A44" r:id="rId85"/>
+    <hyperlink ref="E44" r:id="rId86" location="ResponsibleActorState"/>
+    <hyperlink ref="A45" r:id="rId87"/>
+    <hyperlink ref="E45" r:id="rId88" location="RadioMast"/>
+    <hyperlink ref="A46" r:id="rId89"/>
+    <hyperlink ref="E46" r:id="rId90" location="AccountHolder"/>
+    <hyperlink ref="A47" r:id="rId91"/>
+    <hyperlink ref="E47" r:id="rId92" location="MoneyTransfer"/>
+    <hyperlink ref="A48" r:id="rId93"/>
+    <hyperlink ref="E48" r:id="rId94" location="ResponsibleActorState"/>
+    <hyperlink ref="A49" r:id="rId95"/>
+    <hyperlink ref="E49" r:id="rId96" location="RadioMast"/>
+    <hyperlink ref="A50" r:id="rId97"/>
+    <hyperlink ref="E50" r:id="rId98" location="AccountHolder"/>
+    <hyperlink ref="A51" r:id="rId99"/>
+    <hyperlink ref="E51" r:id="rId100" location="MoneyTransfer"/>
+    <hyperlink ref="A52" r:id="rId101"/>
+    <hyperlink ref="E52" r:id="rId102" location="ResponsibleActorState"/>
+    <hyperlink ref="A53" r:id="rId103"/>
+    <hyperlink ref="E53" r:id="rId104" location="RadioMast"/>
+    <hyperlink ref="A54" r:id="rId105"/>
+    <hyperlink ref="E54" r:id="rId106" location="AccountHolder"/>
+    <hyperlink ref="A55" r:id="rId107"/>
+    <hyperlink ref="E55" r:id="rId108" location="MoneyTransfer"/>
+    <hyperlink ref="A56" r:id="rId109"/>
+    <hyperlink ref="E56" r:id="rId110" location="ResponsibleActorState"/>
+    <hyperlink ref="A57" r:id="rId111"/>
+    <hyperlink ref="E57" r:id="rId112" location="RadioMast"/>
+    <hyperlink ref="A58" r:id="rId113"/>
+    <hyperlink ref="E58" r:id="rId114" location="AccountHolder"/>
+    <hyperlink ref="A59" r:id="rId115"/>
+    <hyperlink ref="E59" r:id="rId116" location="MoneyTransfer"/>
+    <hyperlink ref="A60" r:id="rId117"/>
+    <hyperlink ref="E60" r:id="rId118" location="ResponsibleActorState"/>
+    <hyperlink ref="A61" r:id="rId119"/>
+    <hyperlink ref="E61" r:id="rId120" location="RadioMast"/>
+    <hyperlink ref="A62" r:id="rId121"/>
+    <hyperlink ref="E62" r:id="rId122" location="AccountHolder"/>
+    <hyperlink ref="A63" r:id="rId123"/>
+    <hyperlink ref="E63" r:id="rId124" location="MoneyTransfer"/>
+    <hyperlink ref="A64" r:id="rId125"/>
+    <hyperlink ref="E64" r:id="rId126" location="ResponsibleActorState"/>
+    <hyperlink ref="A65" r:id="rId127"/>
+    <hyperlink ref="E65" r:id="rId128" location="RadioMast"/>
+    <hyperlink ref="A66" r:id="rId129"/>
+    <hyperlink ref="E66" r:id="rId130" location="AccountHolder"/>
+    <hyperlink ref="A67" r:id="rId131"/>
+    <hyperlink ref="E67" r:id="rId132" location="MoneyTransfer"/>
+    <hyperlink ref="A68" r:id="rId133"/>
+    <hyperlink ref="E68" r:id="rId134" location="ResponsibleActorState"/>
+    <hyperlink ref="A69" r:id="rId135"/>
+    <hyperlink ref="E69" r:id="rId136" location="RadioMast"/>
+    <hyperlink ref="A70" r:id="rId137"/>
+    <hyperlink ref="E70" r:id="rId138" location="AccountHolder"/>
+    <hyperlink ref="A71" r:id="rId139"/>
+    <hyperlink ref="E71" r:id="rId140" location="MoneyTransfer"/>
+    <hyperlink ref="A72" r:id="rId141"/>
+    <hyperlink ref="E72" r:id="rId142" location="ResponsibleActorState"/>
+    <hyperlink ref="A73" r:id="rId143"/>
+    <hyperlink ref="E73" r:id="rId144" location="RadioMast"/>
+    <hyperlink ref="A74" r:id="rId145"/>
+    <hyperlink ref="E74" r:id="rId146" location="AccountHolder"/>
+    <hyperlink ref="A75" r:id="rId147"/>
+    <hyperlink ref="E75" r:id="rId148" location="MoneyTransfer"/>
+    <hyperlink ref="A76" r:id="rId149"/>
+    <hyperlink ref="E76" r:id="rId150" location="ResponsibleActorState"/>
+    <hyperlink ref="A77" r:id="rId151"/>
+    <hyperlink ref="E77" r:id="rId152" location="RadioMast"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>